--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH116"/>
+  <dimension ref="A1:BH115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
         <v>5.6</v>
@@ -969,7 +969,7 @@
         <v>5.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
@@ -1002,7 +1002,7 @@
         <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1065,13 +1065,13 @@
         <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
         <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>13</v>
@@ -1080,7 +1080,7 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>13.5</v>
@@ -1092,7 +1092,7 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>15.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
         <v>2.44</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
         <v>3.7</v>
@@ -1957,7 +1957,7 @@
         <v>1.51</v>
       </c>
       <c r="R8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
         <v>2.24</v>
@@ -2014,7 +2014,7 @@
         <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>36</v>
@@ -2026,7 +2026,7 @@
         <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -2065,26 +2065,26 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>27</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.86</v>
       </c>
       <c r="G12" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
         <v>3.95</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>3.15</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
         <v>2.22</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
         <v>2.06</v>
@@ -3482,7 +3482,7 @@
         <v>3.65</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
         <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J19" t="n">
         <v>3.75</v>
@@ -4100,7 +4100,7 @@
         <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4115,16 +4115,16 @@
         <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
         <v>13.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
         <v>12.5</v>
@@ -4133,34 +4133,34 @@
         <v>28</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
         <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
         <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -4169,10 +4169,10 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
@@ -4184,13 +4184,13 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
         <v>17.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
@@ -4199,7 +4199,7 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
         <v>24</v>
@@ -4214,11 +4214,11 @@
         <v>18.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>1.47</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
         <v>4.7</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4646,13 +4646,13 @@
         <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.28</v>
@@ -4670,10 +4670,10 @@
         <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
         <v>2.8</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -4873,7 +4873,7 @@
         <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
         <v>1.95</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
         <v>3.2</v>
       </c>
       <c r="H24" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="I24" t="n">
         <v>3.6</v>
@@ -5040,7 +5040,7 @@
         <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
         <v>2.28</v>
@@ -5813,10 +5813,10 @@
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,31 +6180,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SV Austria Salzburg</t>
+          <t>Kisvarda</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KSV 1919</t>
+          <t>Diosgyori</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="G30" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,31 +6374,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kisvarda</t>
+          <t>SV Austria Salzburg</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diosgyori</t>
+          <t>KSV 1919</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="G31" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -6592,7 +6592,7 @@
         <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
         <v>1.71</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I33" t="n">
         <v>2.82</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K33" t="n">
         <v>4.4</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>1.73</v>
       </c>
       <c r="H34" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I34" t="n">
         <v>5.9</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>12</v>
       </c>
       <c r="Z35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="n">
         <v>110</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G36" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>3.45</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G37" t="n">
         <v>1.74</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I37" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>6.8</v>
       </c>
       <c r="H39" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="I39" t="n">
         <v>1.69</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>1.64</v>
       </c>
       <c r="G40" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H40" t="n">
         <v>5.3</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
         <v>1.81</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8314,109 +8314,109 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="G41" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="H41" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="I41" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="J41" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="O41" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="P41" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="R41" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="S41" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="T41" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="U41" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="V41" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="W41" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="Y41" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z41" t="n">
         <v>14</v>
       </c>
-      <c r="Z41" t="n">
-        <v>15</v>
-      </c>
       <c r="AA41" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB41" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AC41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD41" t="n">
         <v>11</v>
       </c>
       <c r="AE41" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AF41" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AG41" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AH41" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI41" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ41" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AK41" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AL41" t="n">
         <v>42</v>
@@ -8425,68 +8425,68 @@
         <v>65</v>
       </c>
       <c r="AN41" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO41" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP41" t="n">
         <v>22</v>
       </c>
       <c r="AQ41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR41" t="n">
         <v>12</v>
       </c>
-      <c r="AR41" t="n">
-        <v>13</v>
-      </c>
       <c r="AS41" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AT41" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU41" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV41" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW41" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY41" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ41" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BB41" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD41" t="n">
         <v>34</v>
       </c>
-      <c r="BC41" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>24</v>
-      </c>
       <c r="BE41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG41" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8508,179 +8508,179 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4.7</v>
+        <v>2.64</v>
       </c>
       <c r="G42" t="n">
-        <v>4.9</v>
+        <v>2.68</v>
       </c>
       <c r="H42" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="I42" t="n">
-        <v>1.72</v>
+        <v>2.76</v>
       </c>
       <c r="J42" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="K42" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P42" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="R42" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="S42" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="T42" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U42" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH42" t="n">
         <v>14</v>
       </c>
-      <c r="AA42" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="AI42" t="n">
         <v>34</v>
       </c>
-      <c r="AC42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>25</v>
-      </c>
       <c r="AJ42" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AK42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM42" t="n">
         <v>60</v>
       </c>
-      <c r="AL42" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>65</v>
-      </c>
       <c r="AN42" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AP42" t="n">
         <v>22</v>
       </c>
       <c r="AQ42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG42" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8702,179 +8702,179 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.64</v>
+        <v>3.95</v>
       </c>
       <c r="G43" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="I43" t="n">
-        <v>2.76</v>
+        <v>1.96</v>
       </c>
       <c r="J43" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K43" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N43" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="O43" t="n">
         <v>1.19</v>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R43" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S43" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T43" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="U43" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X43" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y43" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z43" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AA43" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AB43" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI43" t="n">
         <v>27</v>
       </c>
-      <c r="AF43" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ43" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AL43" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM43" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN43" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AO43" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="AP43" t="n">
         <v>22</v>
       </c>
       <c r="AQ43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW43" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS43" t="n">
+      <c r="AX43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF43" t="n">
         <v>25</v>
       </c>
-      <c r="AT43" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>12</v>
-      </c>
       <c r="BG43" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8896,61 +8896,61 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FC Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St Pauli</t>
+          <t>Mgladbach</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="G44" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="H44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J44" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K44" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="P44" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="T44" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="U44" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8959,116 +8959,116 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="Z44" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA44" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB44" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD44" t="n">
         <v>14</v>
       </c>
       <c r="AE44" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AF44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG44" t="n">
         <v>12</v>
       </c>
       <c r="AH44" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI44" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM44" t="n">
         <v>60</v>
       </c>
-      <c r="AJ44" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>110</v>
-      </c>
       <c r="AN44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR44" t="n">
         <v>22</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>19.5</v>
       </c>
       <c r="AS44" t="n">
         <v>28</v>
       </c>
       <c r="AT44" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW44" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AX44" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AY44" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA44" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BB44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BD44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE44" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF44" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9090,61 +9090,61 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>FC Heidenheim</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mgladbach</t>
+          <t>St Pauli</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="G45" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="H45" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N45" t="n">
         <v>3.85</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5.2</v>
-      </c>
       <c r="O45" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="P45" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="R45" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="S45" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="T45" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="U45" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -9153,116 +9153,116 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA45" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB45" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD45" t="n">
         <v>14</v>
       </c>
       <c r="AE45" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AF45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG45" t="n">
         <v>12</v>
       </c>
       <c r="AH45" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AJ45" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK45" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AL45" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AM45" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AN45" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP45" t="n">
         <v>13</v>
       </c>
-      <c r="AO45" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ45" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AR45" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AS45" t="n">
         <v>28</v>
       </c>
       <c r="AT45" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV45" t="n">
         <v>12.5</v>
       </c>
-      <c r="AU45" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>12</v>
-      </c>
       <c r="AW45" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX45" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AY45" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BB45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC45" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD45" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE45" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BF45" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
         <v>3.05</v>
       </c>
       <c r="K46" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9323,7 +9323,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q46" t="n">
         <v>2.52</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H47" t="n">
         <v>1.76</v>
@@ -9511,28 +9511,28 @@
         <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O47" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P47" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T47" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U47" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9541,91 +9541,91 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z47" t="n">
         <v>11.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB47" t="n">
         <v>18.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AE47" t="n">
         <v>17</v>
       </c>
       <c r="AF47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG47" t="n">
         <v>18.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI47" t="n">
         <v>28</v>
       </c>
       <c r="AJ47" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK47" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL47" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM47" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN47" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO47" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ47" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR47" t="n">
         <v>10.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT47" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV47" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW47" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX47" t="n">
         <v>32</v>
       </c>
       <c r="AY47" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ47" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA47" t="n">
         <v>25</v>
@@ -9640,17 +9640,17 @@
         <v>48</v>
       </c>
       <c r="BE47" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF47" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BG47" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
         <v>2.54</v>
       </c>
       <c r="H48" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I48" t="n">
         <v>3.15</v>
@@ -9741,7 +9741,7 @@
         <v>13</v>
       </c>
       <c r="Z48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA48" t="n">
         <v>55</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G49" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H49" t="n">
         <v>6.8</v>
@@ -9887,10 +9887,10 @@
         <v>7</v>
       </c>
       <c r="J49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K49" t="n">
         <v>5.4</v>
-      </c>
-      <c r="K49" t="n">
-        <v>5.5</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -9917,10 +9917,10 @@
         <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U49" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -9953,10 +9953,10 @@
         <v>95</v>
       </c>
       <c r="AF49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH49" t="n">
         <v>23</v>
@@ -9965,7 +9965,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK49" t="n">
         <v>15</v>
@@ -9995,10 +9995,10 @@
         <v>46</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU49" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV49" t="n">
         <v>23</v>
@@ -10016,7 +10016,7 @@
         <v>20</v>
       </c>
       <c r="BA49" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BB49" t="n">
         <v>12</v>
@@ -10031,14 +10031,14 @@
         <v>38</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG49" t="n">
         <v>36</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10272,13 +10272,13 @@
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J51" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K51" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10296,7 +10296,7 @@
         <v>1.71</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="H52" t="n">
         <v>3.5</v>
@@ -10472,7 +10472,7 @@
         <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
         <v>2.34</v>
       </c>
       <c r="H53" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I53" t="n">
         <v>4</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10848,13 +10848,13 @@
         <v>3.85</v>
       </c>
       <c r="G54" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J54" t="n">
         <v>3.2</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11042,19 +11042,19 @@
         <v>2.64</v>
       </c>
       <c r="G55" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="H55" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="J55" t="n">
-        <v>2.54</v>
+        <v>3.55</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -11072,7 +11072,7 @@
         <v>1.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -11202,14 +11202,14 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11224,28 +11224,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6.2</v>
+        <v>1.58</v>
       </c>
       <c r="G56" t="n">
-        <v>6.6</v>
+        <v>1.66</v>
       </c>
       <c r="H56" t="n">
-        <v>1.63</v>
+        <v>6.4</v>
       </c>
       <c r="I56" t="n">
-        <v>1.65</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K56" t="n">
         <v>4.5</v>
@@ -11254,31 +11254,31 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R56" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -11287,123 +11287,123 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11418,179 +11418,179 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.58</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="H57" t="n">
-        <v>6.4</v>
+        <v>1.66</v>
       </c>
       <c r="I57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG57" t="n">
         <v>8</v>
       </c>
-      <c r="J57" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>0</v>
-      </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
         <v>1.67</v>
       </c>
       <c r="G59" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H59" t="n">
         <v>4.8</v>
@@ -11845,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q59" t="n">
         <v>1.51</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12009,22 +12009,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="G60" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="H60" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="I60" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="J60" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K60" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="G61" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="H61" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J61" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K61" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12233,10 +12233,10 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G62" t="n">
         <v>2.88</v>
@@ -12412,7 +12412,7 @@
         <v>3.1</v>
       </c>
       <c r="K62" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12591,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G63" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="H63" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="K63" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
         <v>4.5</v>
       </c>
       <c r="J64" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K64" t="n">
         <v>4.2</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
         <v>1.67</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G66" t="n">
         <v>4.5</v>
@@ -13182,13 +13182,13 @@
         <v>2.06</v>
       </c>
       <c r="I66" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J66" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K66" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -13203,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Q66" t="n">
         <v>2.04</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13564,16 +13564,16 @@
         <v>2.52</v>
       </c>
       <c r="G68" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H68" t="n">
         <v>2.62</v>
       </c>
       <c r="I68" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="J68" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K68" t="n">
         <v>4.1</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
         <v>6.4</v>
@@ -13764,13 +13764,13 @@
         <v>1.67</v>
       </c>
       <c r="I69" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J69" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         <v>2.24</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13955,7 +13955,7 @@
         <v>3.2</v>
       </c>
       <c r="H70" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I70" t="n">
         <v>2.6</v>
@@ -13979,7 +13979,7 @@
         <v>1.39</v>
       </c>
       <c r="P70" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q70" t="n">
         <v>2.16</v>
@@ -14006,7 +14006,7 @@
         <v>12.5</v>
       </c>
       <c r="Y70" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z70" t="n">
         <v>16.5</v>
@@ -14024,7 +14024,7 @@
         <v>12.5</v>
       </c>
       <c r="AE70" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF70" t="n">
         <v>23</v>
@@ -14042,7 +14042,7 @@
         <v>60</v>
       </c>
       <c r="AK70" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL70" t="n">
         <v>55</v>
@@ -14060,7 +14060,7 @@
         <v>11</v>
       </c>
       <c r="AQ70" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR70" t="n">
         <v>14</v>
@@ -14078,7 +14078,7 @@
         <v>11</v>
       </c>
       <c r="AW70" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AX70" t="n">
         <v>18.5</v>
@@ -14105,14 +14105,14 @@
         <v>40</v>
       </c>
       <c r="BF70" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG70" t="n">
         <v>23</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14143,22 +14143,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G71" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H71" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I71" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J71" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K71" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -14173,10 +14173,10 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14337,19 +14337,19 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="G72" t="n">
-        <v>1000</v>
+        <v>1.73</v>
       </c>
       <c r="H72" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="I72" t="n">
         <v>1000</v>
       </c>
       <c r="J72" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="K72" t="n">
         <v>1000</v>
@@ -14367,7 +14367,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q72" t="n">
         <v>1.01</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14534,19 +14534,19 @@
         <v>1.51</v>
       </c>
       <c r="G73" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H73" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I73" t="n">
         <v>7.2</v>
       </c>
       <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
         <v>5.1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>5.2</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -14564,10 +14564,10 @@
         <v>2.48</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R73" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S73" t="n">
         <v>2.66</v>
@@ -14609,7 +14609,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG73" t="n">
         <v>9.6</v>
@@ -14657,10 +14657,10 @@
         <v>10.5</v>
       </c>
       <c r="AV73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW73" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX73" t="n">
         <v>9.4</v>
@@ -14681,20 +14681,20 @@
         <v>13.5</v>
       </c>
       <c r="BD73" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE73" t="n">
         <v>65</v>
       </c>
       <c r="BF73" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG73" t="n">
         <v>46</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
         <v>4.5</v>
       </c>
       <c r="H74" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I74" t="n">
         <v>1.87</v>
@@ -14770,7 +14770,7 @@
         <v>1.57</v>
       </c>
       <c r="U74" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -14800,19 +14800,19 @@
         <v>11</v>
       </c>
       <c r="AE74" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF74" t="n">
         <v>40</v>
       </c>
       <c r="AG74" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH74" t="n">
         <v>15.5</v>
       </c>
       <c r="AI74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ74" t="n">
         <v>100</v>
@@ -14827,7 +14827,7 @@
         <v>65</v>
       </c>
       <c r="AN74" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO74" t="n">
         <v>7.6</v>
@@ -14854,13 +14854,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW74" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX74" t="n">
         <v>23</v>
       </c>
       <c r="AY74" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ74" t="n">
         <v>13.5</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v>2.16</v>
       </c>
       <c r="H75" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I75" t="n">
         <v>4</v>
@@ -14961,7 +14961,7 @@
         <v>3.4</v>
       </c>
       <c r="T75" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U75" t="n">
         <v>2.16</v>
@@ -15033,7 +15033,7 @@
         <v>13</v>
       </c>
       <c r="AR75" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AS75" t="n">
         <v>34</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q76" t="n">
         <v>2.74</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G77" t="n">
         <v>1.59</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="G78" t="n">
-        <v>600</v>
+        <v>2.38</v>
       </c>
       <c r="H78" t="n">
         <v>3.7</v>
@@ -15513,10 +15513,10 @@
         <v>6.4</v>
       </c>
       <c r="J78" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="K78" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15531,7 +15531,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q78" t="n">
         <v>2.08</v>
@@ -15664,14 +15664,14 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15686,61 +15686,61 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.48</v>
+        <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>2.66</v>
+        <v>13.5</v>
       </c>
       <c r="H79" t="n">
-        <v>3.7</v>
+        <v>1.29</v>
       </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
-        <v>2.74</v>
+        <v>6.6</v>
       </c>
       <c r="K79" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P79" t="n">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -15749,123 +15749,123 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL79" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO79" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AP79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR79" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AS79" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BB79" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BE79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG79" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -15880,61 +15880,61 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="G80" t="n">
-        <v>13</v>
+        <v>1.18</v>
       </c>
       <c r="H80" t="n">
-        <v>1.3</v>
+        <v>21</v>
       </c>
       <c r="I80" t="n">
-        <v>1.31</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R80" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -15943,123 +15943,123 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AQ80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR80" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS80" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AV80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BC80" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BE80" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BG80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -16074,31 +16074,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="G81" t="n">
-        <v>1.19</v>
+        <v>1.84</v>
       </c>
       <c r="H81" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J81" t="n">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="K81" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16113,10 +16113,10 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -16246,14 +16246,14 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -16263,36 +16263,36 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="G82" t="n">
-        <v>1.84</v>
+        <v>3.95</v>
       </c>
       <c r="H82" t="n">
-        <v>5.2</v>
+        <v>2.16</v>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="J82" t="n">
-        <v>3.65</v>
+        <v>1.58</v>
       </c>
       <c r="K82" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,14 +16440,14 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16462,31 +16462,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="G83" t="n">
-        <v>2.68</v>
+        <v>5.1</v>
       </c>
       <c r="H83" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="I83" t="n">
-        <v>3.95</v>
+        <v>2.36</v>
       </c>
       <c r="J83" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K83" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -16501,10 +16501,10 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -16634,14 +16634,14 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -16656,31 +16656,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="H84" t="n">
-        <v>2.16</v>
+        <v>3.15</v>
       </c>
       <c r="I84" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="J84" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K84" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -16695,10 +16695,10 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -16850,31 +16850,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F85" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J85" t="n">
         <v>3.2</v>
       </c>
-      <c r="G85" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I85" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J85" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K85" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -16889,10 +16889,10 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -17022,14 +17022,14 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -17044,31 +17044,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Nyiregyhaza</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Zalaegerszeg</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G86" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H86" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>3.2</v>
       </c>
       <c r="K86" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -17083,10 +17083,10 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -17216,14 +17216,14 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Hungarian NB I</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -17238,31 +17238,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Nyiregyhaza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Zalaegerszeg</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="G87" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="J87" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K87" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -17277,10 +17277,10 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -17410,14 +17410,14 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -17427,36 +17427,36 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.68</v>
+        <v>3.35</v>
       </c>
       <c r="G88" t="n">
-        <v>2.16</v>
+        <v>3.75</v>
       </c>
       <c r="H88" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K88" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17471,7 +17471,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="Q88" t="n">
         <v>1.66</v>
@@ -17604,14 +17604,14 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17626,31 +17626,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="G89" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H89" t="n">
         <v>3.75</v>
       </c>
-      <c r="H89" t="n">
-        <v>2.04</v>
-      </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K89" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17668,7 +17668,7 @@
         <v>2.24</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,14 +17798,14 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -17815,36 +17815,36 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="G90" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="H90" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J90" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="K90" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17859,10 +17859,10 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -17992,14 +17992,14 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>German Bundesliga 2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18009,36 +18009,36 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>SV Darmstadt</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="G91" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="H91" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="I91" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K91" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -18053,10 +18053,10 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -18186,14 +18186,14 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>German Bundesliga 2</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -18208,31 +18208,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SV Darmstadt</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G92" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
       <c r="I92" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="K92" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18247,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,14 +18380,14 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -18402,31 +18402,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G93" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="H93" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J93" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="K93" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -18574,14 +18574,14 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -18591,191 +18591,191 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="G94" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="H94" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="I94" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J94" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N94" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S94" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U94" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X94" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA94" t="n">
         <v>4.6</v>
       </c>
-      <c r="J94" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K94" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>0</v>
-      </c>
       <c r="BB94" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC94" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD94" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE94" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF94" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG94" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -18790,186 +18790,186 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="G95" t="n">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="H95" t="n">
-        <v>2.02</v>
+        <v>2.96</v>
       </c>
       <c r="I95" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K95" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L95" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="N95" t="n">
-        <v>3.55</v>
+        <v>2.52</v>
       </c>
       <c r="O95" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="P95" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.98</v>
+        <v>2.84</v>
       </c>
       <c r="R95" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S95" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="T95" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="U95" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="V95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y95" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z95" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA95" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AB95" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="AC95" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD95" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AE95" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AF95" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AG95" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AH95" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI95" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ95" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AK95" t="n">
         <v>60</v>
       </c>
       <c r="AL95" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AM95" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="AN95" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO95" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="AP95" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AQ95" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR95" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AS95" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AT95" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AU95" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV95" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AW95" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="AX95" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AY95" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ95" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BA95" t="n">
-        <v>4.6</v>
+        <v>36</v>
       </c>
       <c r="BB95" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="BC95" t="n">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="BD95" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BE95" t="n">
-        <v>4.9</v>
+        <v>48</v>
       </c>
       <c r="BF95" t="n">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="BG95" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -18979,66 +18979,66 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="G96" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="H96" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J96" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K96" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="N96" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="P96" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.84</v>
+        <v>1.91</v>
       </c>
       <c r="R96" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S96" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="T96" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="U96" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -19047,123 +19047,123 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="Y96" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z96" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH96" t="n">
         <v>18</v>
       </c>
-      <c r="AA96" t="n">
+      <c r="AI96" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>990</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO96" t="n">
         <v>60</v>
       </c>
-      <c r="AB96" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD96" t="n">
+      <c r="AP96" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF96" t="n">
         <v>14</v>
       </c>
-      <c r="AE96" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS96" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU96" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV96" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW96" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX96" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY96" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ96" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA96" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB96" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC96" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD96" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE96" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF96" t="n">
-        <v>28</v>
-      </c>
       <c r="BG96" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -19178,61 +19178,61 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>FC Twente</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="G97" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="H97" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I97" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K97" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="R97" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -19241,116 +19241,116 @@
         <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK97" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL97" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM97" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN97" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AO97" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AP97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ97" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR97" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS97" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AT97" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV97" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AW97" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX97" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY97" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ97" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA97" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB97" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BC97" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE97" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BG97" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
         <v>2.72</v>
       </c>
       <c r="G98" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H98" t="n">
         <v>2.68</v>
@@ -19544,14 +19544,14 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -19566,49 +19566,49 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Nublense</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.51</v>
+        <v>2.14</v>
       </c>
       <c r="G99" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J99" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K99" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
         <v>1.58</v>
       </c>
-      <c r="H99" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I99" t="n">
-        <v>8</v>
-      </c>
-      <c r="J99" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K99" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q99" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -19738,14 +19738,14 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -19760,31 +19760,31 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2.04</v>
+        <v>1.41</v>
       </c>
       <c r="G100" t="n">
-        <v>2.66</v>
+        <v>1.46</v>
       </c>
       <c r="H100" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="J100" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="K100" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -19799,10 +19799,10 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -19932,14 +19932,14 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -19949,66 +19949,66 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:05:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FC Twente</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.94</v>
+        <v>3.55</v>
       </c>
       <c r="G101" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="H101" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="I101" t="n">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="J101" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K101" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P101" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -20017,123 +20017,123 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK101" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL101" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM101" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN101" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO101" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP101" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR101" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS101" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU101" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV101" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW101" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX101" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY101" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA101" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB101" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC101" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD101" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE101" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF101" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BG101" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -20143,66 +20143,66 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>16:05:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3.55</v>
+        <v>1.22</v>
       </c>
       <c r="G102" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="H102" t="n">
-        <v>2.12</v>
+        <v>1.09</v>
       </c>
       <c r="I102" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="J102" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R102" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -20211,123 +20211,123 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ102" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL102" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM102" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AN102" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO102" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ102" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AR102" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AS102" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV102" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW102" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AX102" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AY102" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AZ102" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA102" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB102" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BC102" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD102" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BE102" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BF102" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG102" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -20337,36 +20337,36 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="G103" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="H103" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I103" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K103" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -20381,10 +20381,10 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -20514,14 +20514,14 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -20531,36 +20531,36 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="G104" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="H104" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I104" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J104" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="K104" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -20575,10 +20575,10 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -20708,14 +20708,14 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -20725,36 +20725,36 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -20769,10 +20769,10 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -20902,14 +20902,14 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -20919,36 +20919,36 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -20963,10 +20963,10 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -21096,14 +21096,14 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -21113,33 +21113,33 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3.05</v>
+        <v>1.64</v>
       </c>
       <c r="G107" t="n">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="H107" t="n">
-        <v>1.31</v>
+        <v>2.16</v>
       </c>
       <c r="I107" t="n">
-        <v>1.51</v>
+        <v>12</v>
       </c>
       <c r="J107" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="K107" t="n">
         <v>950</v>
@@ -21157,10 +21157,10 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -21290,14 +21290,14 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -21312,31 +21312,31 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1.64</v>
+        <v>2.34</v>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="I108" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K108" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -21351,10 +21351,10 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -21484,14 +21484,14 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -21506,31 +21506,31 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G109" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H109" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="I109" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="J109" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="K109" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -21545,10 +21545,10 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -21678,14 +21678,14 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -21695,36 +21695,36 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1.39</v>
+        <v>3.35</v>
       </c>
       <c r="G110" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="H110" t="n">
         <v>2.52</v>
       </c>
       <c r="I110" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="J110" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="K110" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -21739,10 +21739,10 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -21872,14 +21872,14 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -21889,54 +21889,54 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Tigres</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Mazatlan FC</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3.35</v>
+        <v>1.2</v>
       </c>
       <c r="G111" t="n">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="H111" t="n">
-        <v>2.52</v>
+        <v>16</v>
       </c>
       <c r="I111" t="n">
-        <v>2.86</v>
+        <v>19</v>
       </c>
       <c r="J111" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="K111" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
         <v>3.05</v>
       </c>
-      <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q111" t="n">
-        <v>2.88</v>
+        <v>1.41</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -22100,16 +22100,16 @@
         <v>2.06</v>
       </c>
       <c r="G112" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H112" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I112" t="n">
         <v>3.85</v>
       </c>
       <c r="J112" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K112" t="n">
         <v>4.3</v>
@@ -22130,7 +22130,7 @@
         <v>2.24</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -22260,14 +22260,14 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -22282,31 +22282,31 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mazatlan FC</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -22321,7 +22321,7 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>2.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q113" t="n">
         <v>1.01</v>
@@ -22454,14 +22454,14 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -22471,36 +22471,36 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -22515,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -22648,14 +22648,14 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -22665,36 +22665,36 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -22709,10 +22709,10 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -22842,201 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH116" t="inlineStr">
-        <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
